--- a/tally_templates/SWDN.xlsx
+++ b/tally_templates/SWDN.xlsx
@@ -7090,7 +7090,6 @@
       </c>
       <c r="H54" s="411">
         <f>H12</f>
-        <v>NaN</v>
       </c>
       <c r="I54" s="412" t="s">
         <v>123</v>

--- a/tally_templates/SWDN.xlsx
+++ b/tally_templates/SWDN.xlsx
@@ -1202,7 +1202,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -2733,7 +2733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="648">
+  <cellXfs count="692">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4663,6 +4663,138 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4671,11 +4803,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4943,7 +5075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y131"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5714,7 +5846,7 @@
       <c r="G7" s="338" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="208">
+      <c r="H7" s="663">
         <v>46217</v>
       </c>
       <c r="I7" s="192"/>
@@ -5752,7 +5884,7 @@
       <c r="G8" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="689" t="s">
         <v>110</v>
       </c>
       <c r="I8" s="19"/>
@@ -6948,7 +7080,7 @@
       <c r="G50" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="H50" s="689" t="s">
         <v>110</v>
       </c>
       <c r="I50" s="19"/>
@@ -7073,27 +7205,17 @@
       <c r="Y53" s="201"/>
     </row>
     <row r="54" ht="21" customHeight="1" hidden="1" spans="1:25" s="405" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="406" t="s">
-        <v>121</v>
-      </c>
+      <c r="A54" s="406"/>
       <c r="B54" s="407"/>
-      <c r="C54" s="408" t="s">
-        <v>122</v>
-      </c>
+      <c r="C54" s="408"/>
       <c r="D54" s="409"/>
       <c r="E54" s="409"/>
-      <c r="F54" s="410">
-        <v>14</v>
-      </c>
-      <c r="G54" s="410">
-        <v>14</v>
-      </c>
+      <c r="F54" s="410"/>
+      <c r="G54" s="410"/>
       <c r="H54" s="411">
         <f>H12</f>
       </c>
-      <c r="I54" s="412" t="s">
-        <v>123</v>
-      </c>
+      <c r="I54" s="412"/>
       <c r="J54" s="405"/>
       <c r="K54" s="405"/>
       <c r="L54" s="405"/>
@@ -8168,7 +8290,7 @@
       <c r="G92" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="H92" s="19" t="s">
+      <c r="H92" s="689" t="s">
         <v>110</v>
       </c>
       <c r="I92" s="19"/>
@@ -8293,27 +8415,17 @@
       <c r="Y95" s="5"/>
     </row>
     <row r="96" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A96" s="458" t="s">
-        <v>130</v>
-      </c>
+      <c r="A96" s="458"/>
       <c r="B96" s="459"/>
-      <c r="C96" s="460" t="s">
-        <v>122</v>
-      </c>
+      <c r="C96" s="460"/>
       <c r="D96" s="220"/>
       <c r="E96" s="220"/>
-      <c r="F96" s="461">
-        <v>-25</v>
-      </c>
-      <c r="G96" s="461">
-        <v>-23.4</v>
-      </c>
+      <c r="F96" s="461"/>
+      <c r="G96" s="461"/>
       <c r="H96" s="462" t="s">
         <v>131</v>
       </c>
-      <c r="I96" s="463" t="s">
-        <v>132</v>
-      </c>
+      <c r="I96" s="463"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -8332,27 +8444,15 @@
       <c r="Y96" s="1"/>
     </row>
     <row r="97" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A97" s="464" t="s">
-        <v>133</v>
-      </c>
+      <c r="A97" s="464"/>
       <c r="B97" s="465"/>
-      <c r="C97" s="466" t="s">
-        <v>122</v>
-      </c>
+      <c r="C97" s="466"/>
       <c r="D97" s="399"/>
       <c r="E97" s="399"/>
-      <c r="F97" s="467">
-        <v>-25</v>
-      </c>
-      <c r="G97" s="468">
-        <v>-24.9</v>
-      </c>
-      <c r="H97" s="469" t="s">
-        <v>134</v>
-      </c>
-      <c r="I97" s="470" t="s">
-        <v>132</v>
-      </c>
+      <c r="F97" s="467"/>
+      <c r="G97" s="468"/>
+      <c r="H97" s="469"/>
+      <c r="I97" s="470"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -8371,27 +8471,15 @@
       <c r="Y97" s="1"/>
     </row>
     <row r="98" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A98" s="464" t="s">
-        <v>135</v>
-      </c>
+      <c r="A98" s="464"/>
       <c r="B98" s="465"/>
-      <c r="C98" s="466" t="s">
-        <v>122</v>
-      </c>
+      <c r="C98" s="466"/>
       <c r="D98" s="399"/>
       <c r="E98" s="399"/>
-      <c r="F98" s="467">
-        <v>-25</v>
-      </c>
-      <c r="G98" s="471">
-        <v>-23.1</v>
-      </c>
-      <c r="H98" s="469" t="s">
-        <v>134</v>
-      </c>
-      <c r="I98" s="470" t="s">
-        <v>132</v>
-      </c>
+      <c r="F98" s="467"/>
+      <c r="G98" s="471"/>
+      <c r="H98" s="469"/>
+      <c r="I98" s="470"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -8410,27 +8498,15 @@
       <c r="Y98" s="1"/>
     </row>
     <row r="99" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A99" s="464" t="s">
-        <v>136</v>
-      </c>
+      <c r="A99" s="464"/>
       <c r="B99" s="465"/>
-      <c r="C99" s="466" t="s">
-        <v>122</v>
-      </c>
+      <c r="C99" s="466"/>
       <c r="D99" s="399"/>
       <c r="E99" s="399"/>
-      <c r="F99" s="467">
-        <v>-25</v>
-      </c>
-      <c r="G99" s="471">
-        <v>-23.9</v>
-      </c>
-      <c r="H99" s="469" t="s">
-        <v>134</v>
-      </c>
-      <c r="I99" s="463" t="s">
-        <v>132</v>
-      </c>
+      <c r="F99" s="467"/>
+      <c r="G99" s="471"/>
+      <c r="H99" s="469"/>
+      <c r="I99" s="463"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -8449,27 +8525,15 @@
       <c r="Y99" s="1"/>
     </row>
     <row r="100" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A100" s="420" t="s">
-        <v>137</v>
-      </c>
+      <c r="A100" s="420"/>
       <c r="B100" s="472"/>
-      <c r="C100" s="420" t="s">
-        <v>122</v>
-      </c>
+      <c r="C100" s="420"/>
       <c r="D100" s="473"/>
       <c r="E100" s="473"/>
-      <c r="F100" s="422">
-        <v>-25</v>
-      </c>
-      <c r="G100" s="474">
-        <v>-4.3</v>
-      </c>
-      <c r="H100" s="475" t="s">
-        <v>134</v>
-      </c>
-      <c r="I100" s="424" t="s">
-        <v>132</v>
-      </c>
+      <c r="F100" s="422"/>
+      <c r="G100" s="474"/>
+      <c r="H100" s="475"/>
+      <c r="I100" s="424"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -8488,27 +8552,15 @@
       <c r="Y100" s="1"/>
     </row>
     <row r="101" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A101" s="425" t="s">
-        <v>138</v>
-      </c>
+      <c r="A101" s="425"/>
       <c r="B101" s="459"/>
-      <c r="C101" s="425" t="s">
-        <v>122</v>
-      </c>
+      <c r="C101" s="425"/>
       <c r="D101" s="220"/>
       <c r="E101" s="220"/>
-      <c r="F101" s="426">
-        <v>-25</v>
-      </c>
-      <c r="G101" s="426">
-        <v>-25</v>
-      </c>
-      <c r="H101" s="476" t="s">
-        <v>134</v>
-      </c>
-      <c r="I101" s="428" t="s">
-        <v>132</v>
-      </c>
+      <c r="F101" s="426"/>
+      <c r="G101" s="426"/>
+      <c r="H101" s="476"/>
+      <c r="I101" s="428"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -9455,7 +9507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10253,7 +10305,7 @@
       <c r="A8" s="207" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="209" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="207"/>
@@ -10314,7 +10366,7 @@
       <c r="X9" s="156"/>
       <c r="Y9" s="156"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="212" t="s">
         <v>11</v>
       </c>
@@ -10355,7 +10407,7 @@
       <c r="X10" s="156"/>
       <c r="Y10" s="156"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="215"/>
       <c r="B11" s="215"/>
       <c r="C11" s="277"/>
@@ -11196,7 +11248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11493,7 +11545,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -11553,7 +11605,7 @@
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="648" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5"/>
@@ -11562,13 +11614,13 @@
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="649"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="650"/>
       <c r="L4" s="14"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
@@ -11615,20 +11667,20 @@
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="649"/>
       <c r="C6" s="5"/>
       <c r="D6" s="11"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="649"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="18"/>
+      <c r="K6" s="651"/>
       <c r="L6" s="19" t="s">
         <v>9</v>
       </c>
@@ -14011,7 +14063,7 @@
       <c r="X84" s="5"/>
       <c r="Y84" s="5"/>
     </row>
-    <row r="85" ht="13.5" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="14.9" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="121" t="s">
         <v>21</v>
       </c>
@@ -14630,7 +14682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -15285,7 +15337,7 @@
       <c r="A6" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="41"/>
+      <c r="B6" s="690"/>
       <c r="C6" s="41"/>
       <c r="D6" s="269" t="str">
         <f>'Final Work'!B4</f>
@@ -15304,7 +15356,7 @@
       <c r="O6" s="269" t="s">
         <v>108</v>
       </c>
-      <c r="P6" s="41"/>
+      <c r="P6" s="690"/>
       <c r="Q6" s="41"/>
       <c r="R6" s="201" t="str">
         <f>'Final Work'!G4</f>
@@ -15374,7 +15426,7 @@
       <c r="A8" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="154"/>
+      <c r="B8" s="691"/>
       <c r="C8" s="154"/>
       <c r="D8" s="506" t="s">
         <v>143</v>
@@ -15392,7 +15444,7 @@
       <c r="O8" s="506" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="154"/>
+      <c r="P8" s="691"/>
       <c r="Q8" s="154"/>
       <c r="R8" s="505">
         <f>'Final Work'!G6</f>
@@ -15409,7 +15461,7 @@
       </c>
       <c r="Z8" s="201"/>
       <c r="AA8" s="201"/>
-      <c r="AB8" s="505" t="s">
+      <c r="AB8" s="691" t="s">
         <v>26</v>
       </c>
       <c r="AC8" s="505"/>
@@ -19317,7 +19369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -19957,7 +20009,7 @@
       <c r="A5" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="159" t="s">
+      <c r="B5" s="652" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="119" t="s">
@@ -20022,7 +20074,7 @@
       <c r="A7" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="652" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="161"/>
@@ -20037,7 +20089,7 @@
       <c r="G7" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="163" t="s">
+      <c r="H7" s="653" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="10"/>
@@ -20177,7 +20229,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="169"/>
-      <c r="C12" s="170"/>
+      <c r="C12" s="654"/>
       <c r="D12" s="170"/>
       <c r="E12" s="170"/>
       <c r="F12" s="170"/>
@@ -20204,7 +20256,7 @@
     <row r="13" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="171"/>
       <c r="B13" s="172"/>
-      <c r="C13" s="173"/>
+      <c r="C13" s="655"/>
       <c r="D13" s="173"/>
       <c r="E13" s="173"/>
       <c r="F13" s="173"/>
@@ -20231,7 +20283,7 @@
     <row r="14" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="171"/>
       <c r="B14" s="174"/>
-      <c r="C14" s="175"/>
+      <c r="C14" s="656"/>
       <c r="D14" s="176"/>
       <c r="E14" s="176"/>
       <c r="F14" s="176"/>
@@ -20262,7 +20314,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="174"/>
-      <c r="C15" s="175"/>
+      <c r="C15" s="656"/>
       <c r="D15" s="176"/>
       <c r="E15" s="176"/>
       <c r="F15" s="176"/>
@@ -20289,7 +20341,7 @@
     <row r="16" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="171"/>
       <c r="B16" s="178"/>
-      <c r="C16" s="179"/>
+      <c r="C16" s="657"/>
       <c r="D16" s="180"/>
       <c r="E16" s="180"/>
       <c r="F16" s="180"/>
@@ -20316,7 +20368,7 @@
     <row r="17" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="182"/>
       <c r="B17" s="183"/>
-      <c r="C17" s="184"/>
+      <c r="C17" s="658"/>
       <c r="D17" s="185"/>
       <c r="E17" s="185"/>
       <c r="F17" s="185"/>
@@ -20343,7 +20395,7 @@
     <row r="18" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="187"/>
       <c r="B18" s="174"/>
-      <c r="C18" s="175"/>
+      <c r="C18" s="656"/>
       <c r="D18" s="176"/>
       <c r="E18" s="176"/>
       <c r="F18" s="176"/>
@@ -20370,7 +20422,7 @@
     <row r="19" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="171"/>
       <c r="B19" s="183"/>
-      <c r="C19" s="175"/>
+      <c r="C19" s="656"/>
       <c r="D19" s="176"/>
       <c r="E19" s="176"/>
       <c r="F19" s="176"/>
@@ -20397,7 +20449,7 @@
     <row r="20" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="188"/>
       <c r="B20" s="183"/>
-      <c r="C20" s="175"/>
+      <c r="C20" s="656"/>
       <c r="D20" s="176"/>
       <c r="E20" s="176"/>
       <c r="F20" s="176"/>
@@ -20424,7 +20476,7 @@
     <row r="21" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="189"/>
       <c r="B21" s="178"/>
-      <c r="C21" s="179"/>
+      <c r="C21" s="657"/>
       <c r="D21" s="180"/>
       <c r="E21" s="180"/>
       <c r="F21" s="180"/>
@@ -20451,7 +20503,7 @@
     <row r="22" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="190"/>
       <c r="B22" s="183"/>
-      <c r="C22" s="184"/>
+      <c r="C22" s="658"/>
       <c r="D22" s="185"/>
       <c r="E22" s="185"/>
       <c r="F22" s="185"/>
@@ -20478,7 +20530,7 @@
     <row r="23" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="191"/>
       <c r="B23" s="174"/>
-      <c r="C23" s="175"/>
+      <c r="C23" s="656"/>
       <c r="D23" s="176"/>
       <c r="E23" s="176"/>
       <c r="F23" s="176"/>
@@ -20505,7 +20557,7 @@
     <row r="24" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="171"/>
       <c r="B24" s="174"/>
-      <c r="C24" s="193"/>
+      <c r="C24" s="659"/>
       <c r="D24" s="194"/>
       <c r="E24" s="194"/>
       <c r="F24" s="194"/>
@@ -20532,7 +20584,7 @@
     <row r="25" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="196"/>
       <c r="B25" s="174"/>
-      <c r="C25" s="193"/>
+      <c r="C25" s="659"/>
       <c r="D25" s="194"/>
       <c r="E25" s="194"/>
       <c r="F25" s="194"/>
@@ -20559,7 +20611,7 @@
     <row r="26" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="197"/>
       <c r="B26" s="178"/>
-      <c r="C26" s="179"/>
+      <c r="C26" s="657"/>
       <c r="D26" s="180"/>
       <c r="E26" s="180"/>
       <c r="F26" s="180"/>
@@ -20586,7 +20638,7 @@
     <row r="27" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30"/>
       <c r="B27" s="183"/>
-      <c r="C27" s="193"/>
+      <c r="C27" s="659"/>
       <c r="D27" s="194"/>
       <c r="E27" s="194"/>
       <c r="F27" s="194"/>
@@ -20613,7 +20665,7 @@
     <row r="28" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="171"/>
       <c r="B28" s="174"/>
-      <c r="C28" s="175"/>
+      <c r="C28" s="656"/>
       <c r="D28" s="176"/>
       <c r="E28" s="176"/>
       <c r="F28" s="176"/>
@@ -20640,7 +20692,7 @@
     <row r="29" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="171"/>
       <c r="B29" s="174"/>
-      <c r="C29" s="193"/>
+      <c r="C29" s="659"/>
       <c r="D29" s="194"/>
       <c r="E29" s="194"/>
       <c r="F29" s="194"/>
@@ -20665,9 +20717,9 @@
       <c r="Y29" s="156"/>
     </row>
     <row r="30" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="198"/>
+      <c r="A30" s="660"/>
       <c r="B30" s="174"/>
-      <c r="C30" s="175"/>
+      <c r="C30" s="656"/>
       <c r="D30" s="176"/>
       <c r="E30" s="176"/>
       <c r="F30" s="176"/>
@@ -20692,9 +20744,9 @@
       <c r="Y30" s="156"/>
     </row>
     <row r="31" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="199"/>
+      <c r="A31" s="661"/>
       <c r="B31" s="178"/>
-      <c r="C31" s="175"/>
+      <c r="C31" s="656"/>
       <c r="D31" s="176"/>
       <c r="E31" s="176"/>
       <c r="F31" s="176"/>
@@ -20721,7 +20773,7 @@
     <row r="32" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="30"/>
       <c r="B32" s="28"/>
-      <c r="C32" s="184"/>
+      <c r="C32" s="658"/>
       <c r="D32" s="185"/>
       <c r="E32" s="185"/>
       <c r="F32" s="185"/>
@@ -20748,7 +20800,7 @@
     <row r="33" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="171"/>
       <c r="B33" s="174"/>
-      <c r="C33" s="175"/>
+      <c r="C33" s="656"/>
       <c r="D33" s="176"/>
       <c r="E33" s="176"/>
       <c r="F33" s="176"/>
@@ -20773,9 +20825,9 @@
       <c r="Y33" s="156"/>
     </row>
     <row r="34" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="198"/>
+      <c r="A34" s="660"/>
       <c r="B34" s="174"/>
-      <c r="C34" s="193"/>
+      <c r="C34" s="659"/>
       <c r="D34" s="194"/>
       <c r="E34" s="194"/>
       <c r="F34" s="194"/>
@@ -20800,9 +20852,9 @@
       <c r="Y34" s="156"/>
     </row>
     <row r="35" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="198"/>
+      <c r="A35" s="660"/>
       <c r="B35" s="172"/>
-      <c r="C35" s="175"/>
+      <c r="C35" s="656"/>
       <c r="D35" s="176"/>
       <c r="E35" s="176"/>
       <c r="F35" s="176"/>
@@ -20827,9 +20879,9 @@
       <c r="Y35" s="156"/>
     </row>
     <row r="36" ht="19.9" customHeight="1" spans="1:25" s="156" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="199"/>
+      <c r="A36" s="661"/>
       <c r="B36" s="183"/>
-      <c r="C36" s="200"/>
+      <c r="C36" s="662"/>
       <c r="D36" s="200"/>
       <c r="E36" s="200"/>
       <c r="F36" s="200"/>
@@ -21126,7 +21178,7 @@
       <c r="Y46" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -21160,6 +21212,9 @@
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -21168,7 +21223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -21974,13 +22029,13 @@
       <c r="G6" s="156" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="192"/>
+      <c r="H6" s="209"/>
       <c r="I6" s="192"/>
       <c r="J6" s="156"/>
       <c r="K6" s="156" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="208"/>
+      <c r="L6" s="663"/>
       <c r="M6" s="192"/>
       <c r="N6" s="156"/>
       <c r="O6" s="156"/>
@@ -22026,7 +22081,7 @@
       <c r="A8" s="207" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="156" t="s">
+      <c r="B8" s="664" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="156"/>
@@ -22036,13 +22091,13 @@
       <c r="G8" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="192"/>
+      <c r="H8" s="209"/>
       <c r="I8" s="192"/>
       <c r="J8" s="156"/>
       <c r="K8" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="192"/>
+      <c r="L8" s="209"/>
       <c r="M8" s="192"/>
       <c r="N8" s="156"/>
       <c r="O8" s="156"/>
@@ -22084,7 +22139,7 @@
       <c r="X9" s="156"/>
       <c r="Y9" s="156"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="210" t="s">
         <v>49</v>
       </c>
@@ -22129,7 +22184,7 @@
       <c r="X10" s="156"/>
       <c r="Y10" s="156"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="213"/>
       <c r="B11" s="214"/>
       <c r="C11" s="214"/>
@@ -22159,19 +22214,19 @@
       <c r="Y11" s="156"/>
     </row>
     <row r="12" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="216"/>
+      <c r="A12" s="665"/>
       <c r="B12" s="191"/>
       <c r="C12" s="183"/>
-      <c r="D12" s="217"/>
-      <c r="E12" s="218"/>
-      <c r="F12" s="219"/>
+      <c r="D12" s="666"/>
+      <c r="E12" s="667"/>
+      <c r="F12" s="668"/>
       <c r="G12" s="220"/>
       <c r="H12" s="221"/>
       <c r="I12" s="222"/>
       <c r="J12" s="223"/>
       <c r="K12" s="220"/>
       <c r="L12" s="220"/>
-      <c r="M12" s="224"/>
+      <c r="M12" s="409"/>
       <c r="N12" s="156"/>
       <c r="O12" s="156"/>
       <c r="P12" s="156"/>
@@ -22186,19 +22241,19 @@
       <c r="Y12" s="156"/>
     </row>
     <row r="13" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="225"/>
+      <c r="A13" s="669"/>
       <c r="B13" s="226"/>
       <c r="C13" s="227"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="230"/>
+      <c r="D13" s="670"/>
+      <c r="E13" s="671"/>
+      <c r="F13" s="672"/>
       <c r="G13" s="231"/>
       <c r="H13" s="232"/>
       <c r="I13" s="233"/>
       <c r="J13" s="234"/>
       <c r="K13" s="231"/>
       <c r="L13" s="231"/>
-      <c r="M13" s="235"/>
+      <c r="M13" s="51"/>
       <c r="N13" s="156"/>
       <c r="O13" s="156"/>
       <c r="P13" s="156"/>
@@ -22213,19 +22268,19 @@
       <c r="Y13" s="156"/>
     </row>
     <row r="14" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="225"/>
+      <c r="A14" s="669"/>
       <c r="B14" s="226"/>
       <c r="C14" s="227"/>
-      <c r="D14" s="228"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="230"/>
+      <c r="D14" s="670"/>
+      <c r="E14" s="671"/>
+      <c r="F14" s="672"/>
       <c r="G14" s="231"/>
       <c r="H14" s="232"/>
       <c r="I14" s="233"/>
       <c r="J14" s="234"/>
       <c r="K14" s="231"/>
       <c r="L14" s="231"/>
-      <c r="M14" s="235"/>
+      <c r="M14" s="51"/>
       <c r="N14" s="156"/>
       <c r="O14" s="156"/>
       <c r="P14" s="156"/>
@@ -22240,19 +22295,19 @@
       <c r="Y14" s="156"/>
     </row>
     <row r="15" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="236"/>
+      <c r="A15" s="673"/>
       <c r="B15" s="237"/>
       <c r="C15" s="237"/>
-      <c r="D15" s="238"/>
-      <c r="E15" s="239"/>
-      <c r="F15" s="240"/>
+      <c r="D15" s="674"/>
+      <c r="E15" s="675"/>
+      <c r="F15" s="676"/>
       <c r="G15" s="237"/>
       <c r="H15" s="241"/>
       <c r="I15" s="242"/>
       <c r="J15" s="241"/>
       <c r="K15" s="237"/>
       <c r="L15" s="237"/>
-      <c r="M15" s="235"/>
+      <c r="M15" s="51"/>
       <c r="N15" s="156"/>
       <c r="O15" s="156"/>
       <c r="P15" s="156"/>
@@ -22267,19 +22322,19 @@
       <c r="Y15" s="156"/>
     </row>
     <row r="16" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="236"/>
+      <c r="A16" s="673"/>
       <c r="B16" s="237"/>
       <c r="C16" s="237"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="240"/>
+      <c r="D16" s="674"/>
+      <c r="E16" s="675"/>
+      <c r="F16" s="676"/>
       <c r="G16" s="237"/>
       <c r="H16" s="241"/>
       <c r="I16" s="242"/>
       <c r="J16" s="241"/>
       <c r="K16" s="237"/>
       <c r="L16" s="237"/>
-      <c r="M16" s="243"/>
+      <c r="M16" s="62"/>
       <c r="N16" s="156"/>
       <c r="O16" s="156"/>
       <c r="P16" s="156"/>
@@ -22294,19 +22349,19 @@
       <c r="Y16" s="156"/>
     </row>
     <row r="17" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="236"/>
+      <c r="A17" s="673"/>
       <c r="B17" s="237"/>
       <c r="C17" s="237"/>
-      <c r="D17" s="238"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="240"/>
+      <c r="D17" s="674"/>
+      <c r="E17" s="675"/>
+      <c r="F17" s="676"/>
       <c r="G17" s="237"/>
       <c r="H17" s="241"/>
       <c r="I17" s="242"/>
       <c r="J17" s="241"/>
       <c r="K17" s="237"/>
       <c r="L17" s="237"/>
-      <c r="M17" s="244"/>
+      <c r="M17" s="677"/>
       <c r="N17" s="156"/>
       <c r="O17" s="156"/>
       <c r="P17" s="156"/>
@@ -22321,19 +22376,19 @@
       <c r="Y17" s="156"/>
     </row>
     <row r="18" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="236"/>
+      <c r="A18" s="673"/>
       <c r="B18" s="237"/>
       <c r="C18" s="237"/>
-      <c r="D18" s="238"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="240"/>
+      <c r="D18" s="674"/>
+      <c r="E18" s="675"/>
+      <c r="F18" s="676"/>
       <c r="G18" s="237"/>
       <c r="H18" s="241"/>
       <c r="I18" s="242"/>
       <c r="J18" s="241"/>
       <c r="K18" s="237"/>
       <c r="L18" s="237"/>
-      <c r="M18" s="244"/>
+      <c r="M18" s="677"/>
       <c r="N18" s="156"/>
       <c r="O18" s="156"/>
       <c r="P18" s="156"/>
@@ -22348,19 +22403,19 @@
       <c r="Y18" s="156"/>
     </row>
     <row r="19" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="236"/>
+      <c r="A19" s="673"/>
       <c r="B19" s="237"/>
       <c r="C19" s="237"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="239"/>
-      <c r="F19" s="240"/>
+      <c r="D19" s="674"/>
+      <c r="E19" s="675"/>
+      <c r="F19" s="676"/>
       <c r="G19" s="237"/>
       <c r="H19" s="241"/>
       <c r="I19" s="242"/>
       <c r="J19" s="241"/>
       <c r="K19" s="237"/>
       <c r="L19" s="237"/>
-      <c r="M19" s="244"/>
+      <c r="M19" s="677"/>
       <c r="N19" s="156"/>
       <c r="O19" s="156"/>
       <c r="P19" s="156"/>
@@ -22375,19 +22430,19 @@
       <c r="Y19" s="156"/>
     </row>
     <row r="20" ht="19.9" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="236"/>
+      <c r="A20" s="673"/>
       <c r="B20" s="237"/>
       <c r="C20" s="237"/>
-      <c r="D20" s="238"/>
-      <c r="E20" s="239"/>
-      <c r="F20" s="240"/>
+      <c r="D20" s="674"/>
+      <c r="E20" s="675"/>
+      <c r="F20" s="676"/>
       <c r="G20" s="237"/>
       <c r="H20" s="241"/>
       <c r="I20" s="242"/>
       <c r="J20" s="241"/>
       <c r="K20" s="237"/>
       <c r="L20" s="237"/>
-      <c r="M20" s="244"/>
+      <c r="M20" s="677"/>
       <c r="N20" s="156"/>
       <c r="O20" s="156"/>
       <c r="P20" s="156"/>
@@ -22402,19 +22457,19 @@
       <c r="Y20" s="156"/>
     </row>
     <row r="21" ht="19.9" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="236"/>
+      <c r="A21" s="673"/>
       <c r="B21" s="237"/>
       <c r="C21" s="237"/>
-      <c r="D21" s="238"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="240"/>
+      <c r="D21" s="674"/>
+      <c r="E21" s="675"/>
+      <c r="F21" s="676"/>
       <c r="G21" s="237"/>
       <c r="H21" s="241"/>
       <c r="I21" s="242"/>
       <c r="J21" s="241"/>
       <c r="K21" s="237"/>
       <c r="L21" s="237"/>
-      <c r="M21" s="244"/>
+      <c r="M21" s="677"/>
       <c r="N21" s="156"/>
       <c r="O21" s="156"/>
       <c r="P21" s="156"/>
@@ -22429,19 +22484,19 @@
       <c r="Y21" s="156"/>
     </row>
     <row r="22" ht="19.9" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="236"/>
+      <c r="A22" s="673"/>
       <c r="B22" s="237"/>
       <c r="C22" s="237"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="239"/>
-      <c r="F22" s="240"/>
+      <c r="D22" s="674"/>
+      <c r="E22" s="675"/>
+      <c r="F22" s="676"/>
       <c r="G22" s="237"/>
       <c r="H22" s="241"/>
       <c r="I22" s="242"/>
       <c r="J22" s="241"/>
       <c r="K22" s="237"/>
       <c r="L22" s="237"/>
-      <c r="M22" s="244"/>
+      <c r="M22" s="677"/>
       <c r="N22" s="156"/>
       <c r="O22" s="156"/>
       <c r="P22" s="156"/>
@@ -23087,7 +23142,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -23892,13 +23947,13 @@
       <c r="G6" s="156" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="192"/>
+      <c r="H6" s="209"/>
       <c r="I6" s="192"/>
       <c r="J6" s="156"/>
       <c r="K6" s="156" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="208"/>
+      <c r="L6" s="663"/>
       <c r="M6" s="192"/>
       <c r="N6" s="5"/>
       <c r="O6" s="156"/>
@@ -23944,7 +23999,7 @@
       <c r="A8" s="207" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="156" t="s">
+      <c r="B8" s="664" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="294"/>
@@ -23954,13 +24009,13 @@
       <c r="G8" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="192"/>
+      <c r="H8" s="209"/>
       <c r="I8" s="192"/>
       <c r="J8" s="156"/>
       <c r="K8" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="192"/>
+      <c r="L8" s="209"/>
       <c r="M8" s="192"/>
       <c r="N8" s="156"/>
       <c r="O8" s="156"/>
@@ -24002,7 +24057,7 @@
       <c r="X9" s="156"/>
       <c r="Y9" s="156"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="210" t="s">
         <v>49</v>
       </c>
@@ -24047,7 +24102,7 @@
       <c r="X10" s="156"/>
       <c r="Y10" s="156"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="213"/>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
@@ -24077,19 +24132,19 @@
       <c r="Y11" s="156"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="295"/>
+      <c r="A12" s="678"/>
       <c r="B12" s="296"/>
       <c r="C12" s="296"/>
-      <c r="D12" s="297"/>
-      <c r="E12" s="298"/>
-      <c r="F12" s="299"/>
+      <c r="D12" s="679"/>
+      <c r="E12" s="680"/>
+      <c r="F12" s="681"/>
       <c r="G12" s="296"/>
       <c r="H12" s="300"/>
       <c r="I12" s="301"/>
       <c r="J12" s="300"/>
       <c r="K12" s="296"/>
       <c r="L12" s="296"/>
-      <c r="M12" s="302"/>
+      <c r="M12" s="46"/>
       <c r="N12" s="156"/>
       <c r="O12" s="156"/>
       <c r="P12" s="156"/>
@@ -24104,19 +24159,19 @@
       <c r="Y12" s="156"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="225"/>
+      <c r="A13" s="669"/>
       <c r="B13" s="237"/>
       <c r="C13" s="237"/>
-      <c r="D13" s="238"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="240"/>
+      <c r="D13" s="674"/>
+      <c r="E13" s="675"/>
+      <c r="F13" s="676"/>
       <c r="G13" s="237"/>
       <c r="H13" s="241"/>
       <c r="I13" s="242"/>
       <c r="J13" s="241"/>
       <c r="K13" s="237"/>
       <c r="L13" s="237"/>
-      <c r="M13" s="303"/>
+      <c r="M13" s="65"/>
       <c r="N13" s="156"/>
       <c r="O13" s="156"/>
       <c r="P13" s="156"/>
@@ -24131,19 +24186,19 @@
       <c r="Y13" s="156"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="236"/>
+      <c r="A14" s="673"/>
       <c r="B14" s="237"/>
       <c r="C14" s="237"/>
-      <c r="D14" s="238"/>
-      <c r="E14" s="239"/>
-      <c r="F14" s="240"/>
+      <c r="D14" s="674"/>
+      <c r="E14" s="675"/>
+      <c r="F14" s="676"/>
       <c r="G14" s="237"/>
       <c r="H14" s="241"/>
       <c r="I14" s="242"/>
       <c r="J14" s="241"/>
       <c r="K14" s="237"/>
       <c r="L14" s="237"/>
-      <c r="M14" s="304"/>
+      <c r="M14" s="54"/>
       <c r="N14" s="156"/>
       <c r="O14" s="156"/>
       <c r="P14" s="156"/>
@@ -24158,19 +24213,19 @@
       <c r="Y14" s="156"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="236"/>
+      <c r="A15" s="673"/>
       <c r="B15" s="237"/>
       <c r="C15" s="237"/>
-      <c r="D15" s="238"/>
-      <c r="E15" s="239"/>
-      <c r="F15" s="240"/>
+      <c r="D15" s="674"/>
+      <c r="E15" s="675"/>
+      <c r="F15" s="676"/>
       <c r="G15" s="237"/>
       <c r="H15" s="241"/>
       <c r="I15" s="242"/>
       <c r="J15" s="241"/>
       <c r="K15" s="237"/>
       <c r="L15" s="237"/>
-      <c r="M15" s="304"/>
+      <c r="M15" s="54"/>
       <c r="N15" s="156"/>
       <c r="O15" s="156"/>
       <c r="P15" s="156"/>
@@ -24185,19 +24240,19 @@
       <c r="Y15" s="156"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="236"/>
+      <c r="A16" s="673"/>
       <c r="B16" s="237"/>
       <c r="C16" s="237"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="240"/>
+      <c r="D16" s="674"/>
+      <c r="E16" s="675"/>
+      <c r="F16" s="676"/>
       <c r="G16" s="237"/>
       <c r="H16" s="241"/>
       <c r="I16" s="242"/>
       <c r="J16" s="241"/>
       <c r="K16" s="237"/>
       <c r="L16" s="237"/>
-      <c r="M16" s="304"/>
+      <c r="M16" s="54"/>
       <c r="N16" s="156"/>
       <c r="O16" s="156"/>
       <c r="P16" s="156"/>
@@ -24212,19 +24267,19 @@
       <c r="Y16" s="156"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="236"/>
+      <c r="A17" s="673"/>
       <c r="B17" s="237"/>
       <c r="C17" s="237"/>
-      <c r="D17" s="238"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="240"/>
+      <c r="D17" s="674"/>
+      <c r="E17" s="675"/>
+      <c r="F17" s="676"/>
       <c r="G17" s="237"/>
       <c r="H17" s="241"/>
       <c r="I17" s="242"/>
       <c r="J17" s="241"/>
       <c r="K17" s="237"/>
       <c r="L17" s="237"/>
-      <c r="M17" s="304"/>
+      <c r="M17" s="54"/>
       <c r="N17" s="156"/>
       <c r="O17" s="156"/>
       <c r="P17" s="156"/>
@@ -24239,19 +24294,19 @@
       <c r="Y17" s="156"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="236"/>
+      <c r="A18" s="673"/>
       <c r="B18" s="237"/>
       <c r="C18" s="237"/>
-      <c r="D18" s="238"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="240"/>
+      <c r="D18" s="674"/>
+      <c r="E18" s="675"/>
+      <c r="F18" s="676"/>
       <c r="G18" s="237"/>
       <c r="H18" s="241"/>
       <c r="I18" s="242"/>
       <c r="J18" s="241"/>
       <c r="K18" s="237"/>
       <c r="L18" s="237"/>
-      <c r="M18" s="304"/>
+      <c r="M18" s="54"/>
       <c r="N18" s="156"/>
       <c r="O18" s="156"/>
       <c r="P18" s="156"/>
@@ -24266,19 +24321,19 @@
       <c r="Y18" s="156"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="236"/>
+      <c r="A19" s="673"/>
       <c r="B19" s="237"/>
       <c r="C19" s="237"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="239"/>
-      <c r="F19" s="240"/>
+      <c r="D19" s="674"/>
+      <c r="E19" s="675"/>
+      <c r="F19" s="676"/>
       <c r="G19" s="237"/>
       <c r="H19" s="241"/>
       <c r="I19" s="242"/>
       <c r="J19" s="241"/>
       <c r="K19" s="237"/>
       <c r="L19" s="237"/>
-      <c r="M19" s="304"/>
+      <c r="M19" s="54"/>
       <c r="N19" s="156"/>
       <c r="O19" s="156"/>
       <c r="P19" s="156"/>
@@ -24293,19 +24348,19 @@
       <c r="Y19" s="156"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="236"/>
+      <c r="A20" s="673"/>
       <c r="B20" s="237"/>
       <c r="C20" s="237"/>
-      <c r="D20" s="238"/>
-      <c r="E20" s="239"/>
-      <c r="F20" s="240"/>
+      <c r="D20" s="674"/>
+      <c r="E20" s="675"/>
+      <c r="F20" s="676"/>
       <c r="G20" s="237"/>
       <c r="H20" s="241"/>
       <c r="I20" s="242"/>
       <c r="J20" s="241"/>
       <c r="K20" s="237"/>
       <c r="L20" s="237"/>
-      <c r="M20" s="304"/>
+      <c r="M20" s="54"/>
       <c r="N20" s="156"/>
       <c r="O20" s="156"/>
       <c r="P20" s="156"/>
@@ -24320,19 +24375,19 @@
       <c r="Y20" s="156"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="305"/>
+      <c r="A21" s="682"/>
       <c r="B21" s="306"/>
       <c r="C21" s="306"/>
-      <c r="D21" s="307"/>
-      <c r="E21" s="308"/>
-      <c r="F21" s="309"/>
+      <c r="D21" s="683"/>
+      <c r="E21" s="684"/>
+      <c r="F21" s="685"/>
       <c r="G21" s="306"/>
       <c r="H21" s="310"/>
       <c r="I21" s="311"/>
       <c r="J21" s="310"/>
       <c r="K21" s="306"/>
       <c r="L21" s="306"/>
-      <c r="M21" s="312"/>
+      <c r="M21" s="92"/>
       <c r="N21" s="156"/>
       <c r="O21" s="156"/>
       <c r="P21" s="156"/>
@@ -24347,19 +24402,19 @@
       <c r="Y21" s="156"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="236"/>
+      <c r="A22" s="673"/>
       <c r="B22" s="237"/>
       <c r="C22" s="237"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="239"/>
-      <c r="F22" s="240"/>
+      <c r="D22" s="674"/>
+      <c r="E22" s="675"/>
+      <c r="F22" s="676"/>
       <c r="G22" s="237"/>
       <c r="H22" s="313"/>
       <c r="I22" s="314"/>
       <c r="J22" s="241"/>
       <c r="K22" s="237"/>
       <c r="L22" s="237"/>
-      <c r="M22" s="315"/>
+      <c r="M22" s="399"/>
       <c r="N22" s="156"/>
       <c r="O22" s="156"/>
       <c r="P22" s="156"/>
@@ -24374,19 +24429,19 @@
       <c r="Y22" s="156"/>
     </row>
     <row r="23" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="236"/>
+      <c r="A23" s="673"/>
       <c r="B23" s="237"/>
       <c r="C23" s="237"/>
-      <c r="D23" s="238"/>
-      <c r="E23" s="239"/>
-      <c r="F23" s="240"/>
+      <c r="D23" s="674"/>
+      <c r="E23" s="675"/>
+      <c r="F23" s="676"/>
       <c r="G23" s="237"/>
       <c r="H23" s="241"/>
       <c r="I23" s="242"/>
       <c r="J23" s="241"/>
       <c r="K23" s="237"/>
       <c r="L23" s="237"/>
-      <c r="M23" s="304"/>
+      <c r="M23" s="54"/>
       <c r="N23" s="156"/>
       <c r="O23" s="156"/>
       <c r="P23" s="156"/>
@@ -24401,19 +24456,19 @@
       <c r="Y23" s="156"/>
     </row>
     <row r="24" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="236"/>
+      <c r="A24" s="673"/>
       <c r="B24" s="237"/>
       <c r="C24" s="237"/>
-      <c r="D24" s="238"/>
-      <c r="E24" s="239"/>
-      <c r="F24" s="240"/>
+      <c r="D24" s="674"/>
+      <c r="E24" s="675"/>
+      <c r="F24" s="676"/>
       <c r="G24" s="237"/>
       <c r="H24" s="241"/>
       <c r="I24" s="242"/>
       <c r="J24" s="241"/>
       <c r="K24" s="237"/>
       <c r="L24" s="237"/>
-      <c r="M24" s="304"/>
+      <c r="M24" s="54"/>
       <c r="N24" s="156"/>
       <c r="O24" s="156"/>
       <c r="P24" s="156"/>
@@ -24975,7 +25030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -25772,7 +25827,7 @@
       <c r="A8" s="207" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="209" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="207"/>
@@ -25833,7 +25888,7 @@
       <c r="X9" s="156"/>
       <c r="Y9" s="156"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="210" t="s">
         <v>11</v>
       </c>
@@ -25874,7 +25929,7 @@
       <c r="X10" s="156"/>
       <c r="Y10" s="156"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="213"/>
       <c r="B11" s="213"/>
       <c r="C11" s="277"/>
@@ -26745,7 +26800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -27422,7 +27477,7 @@
       <c r="F4" s="336" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="208"/>
+      <c r="G4" s="663"/>
       <c r="H4" s="192"/>
       <c r="I4" s="156"/>
       <c r="J4" s="156"/>
@@ -27482,7 +27537,7 @@
       <c r="F6" s="336" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="335" t="s">
+      <c r="G6" s="686" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="156"/>
@@ -28125,12 +28180,12 @@
     <row r="29" ht="23.1" customHeight="1" spans="1:25" s="342" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="360"/>
       <c r="B29" s="361"/>
-      <c r="C29" s="379"/>
-      <c r="D29" s="379"/>
-      <c r="E29" s="379"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="379"/>
-      <c r="H29" s="379"/>
+      <c r="C29" s="687"/>
+      <c r="D29" s="687"/>
+      <c r="E29" s="687"/>
+      <c r="F29" s="688"/>
+      <c r="G29" s="687"/>
+      <c r="H29" s="687"/>
       <c r="I29" s="342"/>
       <c r="J29" s="342"/>
       <c r="K29" s="342"/>
@@ -28152,12 +28207,12 @@
     <row r="30" ht="23.1" customHeight="1" spans="1:25" s="342" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="360"/>
       <c r="B30" s="361"/>
-      <c r="C30" s="379"/>
-      <c r="D30" s="379"/>
-      <c r="E30" s="379"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="379"/>
-      <c r="H30" s="379"/>
+      <c r="C30" s="687"/>
+      <c r="D30" s="687"/>
+      <c r="E30" s="687"/>
+      <c r="F30" s="688"/>
+      <c r="G30" s="687"/>
+      <c r="H30" s="687"/>
       <c r="I30" s="342"/>
       <c r="J30" s="342"/>
       <c r="K30" s="342"/>
@@ -28179,12 +28234,12 @@
     <row r="31" ht="23.1" customHeight="1" spans="1:25" s="342" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="360"/>
       <c r="B31" s="361"/>
-      <c r="C31" s="379"/>
-      <c r="D31" s="379"/>
-      <c r="E31" s="379"/>
-      <c r="F31" s="380"/>
-      <c r="G31" s="379"/>
-      <c r="H31" s="379"/>
+      <c r="C31" s="687"/>
+      <c r="D31" s="687"/>
+      <c r="E31" s="687"/>
+      <c r="F31" s="688"/>
+      <c r="G31" s="687"/>
+      <c r="H31" s="687"/>
       <c r="I31" s="342"/>
       <c r="J31" s="342"/>
       <c r="K31" s="342"/>
@@ -28546,7 +28601,7 @@
       <c r="F43" s="336" t="s">
         <v>85</v>
       </c>
-      <c r="G43" s="335" t="s">
+      <c r="G43" s="686" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="156"/>
@@ -28728,24 +28783,14 @@
       <c r="Y48" s="342"/>
     </row>
     <row r="49" ht="23.1" customHeight="1" spans="1:25" s="342" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="353" t="s">
-        <v>101</v>
-      </c>
+      <c r="A49" s="353"/>
       <c r="B49" s="353"/>
-      <c r="C49" s="386" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="355" t="s">
-        <v>15</v>
-      </c>
+      <c r="C49" s="386"/>
+      <c r="D49" s="355"/>
       <c r="E49" s="355"/>
-      <c r="F49" s="387" t="s">
-        <v>103</v>
-      </c>
+      <c r="F49" s="387"/>
       <c r="G49" s="355"/>
-      <c r="H49" s="355" t="s">
-        <v>104</v>
-      </c>
+      <c r="H49" s="355"/>
       <c r="I49" s="342"/>
       <c r="J49" s="342"/>
       <c r="K49" s="342"/>
